--- a/artfynd/A 21423-2024 artfynd.xlsx
+++ b/artfynd/A 21423-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118916046</v>
+        <v>118916043</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567276</v>
+        <v>567305</v>
       </c>
       <c r="R2" t="n">
-        <v>7241770</v>
+        <v>7241760</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118916051</v>
+        <v>118916062</v>
       </c>
       <c r="B3" t="n">
-        <v>90522</v>
+        <v>97867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567260</v>
+        <v>567401</v>
       </c>
       <c r="R3" t="n">
-        <v>7241978</v>
+        <v>7241831</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118916055</v>
+        <v>118916060</v>
       </c>
       <c r="B4" t="n">
-        <v>96801</v>
+        <v>57306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567358</v>
+        <v>567388</v>
       </c>
       <c r="R4" t="n">
-        <v>7241959</v>
+        <v>7241872</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118916047</v>
+        <v>118916057</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567264</v>
+        <v>567355</v>
       </c>
       <c r="R5" t="n">
-        <v>7241789</v>
+        <v>7241955</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118916060</v>
+        <v>118916051</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>90522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1149,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567388</v>
+        <v>567260</v>
       </c>
       <c r="R6" t="n">
-        <v>7241872</v>
+        <v>7241978</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118916044</v>
+        <v>118916053</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>96807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,43 +1257,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567298</v>
+        <v>567358</v>
       </c>
       <c r="R7" t="n">
-        <v>7241769</v>
+        <v>7241988</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118916043</v>
+        <v>118916045</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567305</v>
+        <v>567294</v>
       </c>
       <c r="R8" t="n">
-        <v>7241760</v>
+        <v>7241774</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1596,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916062</v>
+        <v>118916047</v>
       </c>
       <c r="B10" t="n">
-        <v>97867</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1593,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567401</v>
+        <v>567264</v>
       </c>
       <c r="R10" t="n">
-        <v>7241831</v>
+        <v>7241789</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1820,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916053</v>
+        <v>118916044</v>
       </c>
       <c r="B12" t="n">
-        <v>96807</v>
+        <v>57290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,38 +1822,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567358</v>
+        <v>567298</v>
       </c>
       <c r="R12" t="n">
-        <v>7241988</v>
+        <v>7241769</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1895,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916049</v>
+        <v>118916055</v>
       </c>
       <c r="B13" t="n">
-        <v>57306</v>
+        <v>96801</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,43 +1939,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567260</v>
+        <v>567358</v>
       </c>
       <c r="R13" t="n">
-        <v>7241978</v>
+        <v>7241959</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2012,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916045</v>
+        <v>118916049</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2065,34 +2055,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567294</v>
+        <v>567260</v>
       </c>
       <c r="R14" t="n">
-        <v>7241774</v>
+        <v>7241978</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2124,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916057</v>
+        <v>118916046</v>
       </c>
       <c r="B15" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,34 +2172,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567355</v>
+        <v>567276</v>
       </c>
       <c r="R15" t="n">
-        <v>7241955</v>
+        <v>7241770</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 21423-2024 artfynd.xlsx
+++ b/artfynd/A 21423-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118916043</v>
+        <v>118916045</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567305</v>
+        <v>567294</v>
       </c>
       <c r="R2" t="n">
-        <v>7241760</v>
+        <v>7241774</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118916062</v>
+        <v>118916051</v>
       </c>
       <c r="B3" t="n">
-        <v>97867</v>
+        <v>90529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567401</v>
+        <v>567260</v>
       </c>
       <c r="R3" t="n">
-        <v>7241831</v>
+        <v>7241978</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118916060</v>
+        <v>118916044</v>
       </c>
       <c r="B4" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567388</v>
+        <v>567298</v>
       </c>
       <c r="R4" t="n">
-        <v>7241872</v>
+        <v>7241769</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118916057</v>
+        <v>118916046</v>
       </c>
       <c r="B5" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567355</v>
+        <v>567276</v>
       </c>
       <c r="R5" t="n">
-        <v>7241955</v>
+        <v>7241770</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118916051</v>
+        <v>118916055</v>
       </c>
       <c r="B6" t="n">
-        <v>90522</v>
+        <v>96808</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1145,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567260</v>
+        <v>567358</v>
       </c>
       <c r="R6" t="n">
-        <v>7241978</v>
+        <v>7241959</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118916053</v>
+        <v>118916057</v>
       </c>
       <c r="B7" t="n">
-        <v>96807</v>
+        <v>90529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1257,25 +1257,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567358</v>
+        <v>567355</v>
       </c>
       <c r="R7" t="n">
-        <v>7241988</v>
+        <v>7241955</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118916045</v>
+        <v>118916043</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1373,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567294</v>
+        <v>567305</v>
       </c>
       <c r="R8" t="n">
-        <v>7241774</v>
+        <v>7241760</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118916052</v>
+        <v>118916047</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567274</v>
+        <v>567264</v>
       </c>
       <c r="R9" t="n">
-        <v>7241984</v>
+        <v>7241789</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916047</v>
+        <v>118916052</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,39 +1607,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567264</v>
+        <v>567274</v>
       </c>
       <c r="R10" t="n">
-        <v>7241789</v>
+        <v>7241984</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,7 +1706,7 @@
         <v>118916054</v>
       </c>
       <c r="B11" t="n">
-        <v>97867</v>
+        <v>97874</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916044</v>
+        <v>118916062</v>
       </c>
       <c r="B12" t="n">
-        <v>57290</v>
+        <v>97874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,43 +1827,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567298</v>
+        <v>567401</v>
       </c>
       <c r="R12" t="n">
-        <v>7241769</v>
+        <v>7241831</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916055</v>
+        <v>118916053</v>
       </c>
       <c r="B13" t="n">
-        <v>96801</v>
+        <v>96814</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,16 +1943,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1970,7 +1970,7 @@
         <v>567358</v>
       </c>
       <c r="R13" t="n">
-        <v>7241959</v>
+        <v>7241988</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,7 +2039,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916049</v>
+        <v>118916060</v>
       </c>
       <c r="B14" t="n">
         <v>57306</v>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567260</v>
+        <v>567388</v>
       </c>
       <c r="R14" t="n">
-        <v>7241978</v>
+        <v>7241872</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916046</v>
+        <v>118916049</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567276</v>
+        <v>567260</v>
       </c>
       <c r="R15" t="n">
-        <v>7241770</v>
+        <v>7241978</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 21423-2024 artfynd.xlsx
+++ b/artfynd/A 21423-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118916045</v>
+        <v>118916046</v>
       </c>
       <c r="B2" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567294</v>
+        <v>567276</v>
       </c>
       <c r="R2" t="n">
-        <v>7241774</v>
+        <v>7241770</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118916051</v>
+        <v>118916054</v>
       </c>
       <c r="B3" t="n">
-        <v>90529</v>
+        <v>97874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567260</v>
+        <v>567357</v>
       </c>
       <c r="R3" t="n">
-        <v>7241978</v>
+        <v>7241980</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118916044</v>
+        <v>118916051</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567298</v>
+        <v>567260</v>
       </c>
       <c r="R4" t="n">
-        <v>7241769</v>
+        <v>7241978</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118916046</v>
+        <v>118916057</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567276</v>
+        <v>567355</v>
       </c>
       <c r="R5" t="n">
-        <v>7241770</v>
+        <v>7241955</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118916055</v>
+        <v>118916062</v>
       </c>
       <c r="B6" t="n">
-        <v>96808</v>
+        <v>97874</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567358</v>
+        <v>567401</v>
       </c>
       <c r="R6" t="n">
-        <v>7241959</v>
+        <v>7241831</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118916057</v>
+        <v>118916060</v>
       </c>
       <c r="B7" t="n">
-        <v>90529</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567355</v>
+        <v>567388</v>
       </c>
       <c r="R7" t="n">
-        <v>7241955</v>
+        <v>7241872</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118916047</v>
+        <v>118916049</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>57306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1510,7 +1510,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567264</v>
+        <v>567260</v>
       </c>
       <c r="R9" t="n">
-        <v>7241789</v>
+        <v>7241978</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916052</v>
+        <v>118916055</v>
       </c>
       <c r="B10" t="n">
-        <v>78491</v>
+        <v>96808</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,25 +1603,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567274</v>
+        <v>567358</v>
       </c>
       <c r="R10" t="n">
-        <v>7241984</v>
+        <v>7241959</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916054</v>
+        <v>118916044</v>
       </c>
       <c r="B11" t="n">
-        <v>97874</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,38 +1715,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567357</v>
+        <v>567298</v>
       </c>
       <c r="R11" t="n">
-        <v>7241980</v>
+        <v>7241769</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916062</v>
+        <v>118916053</v>
       </c>
       <c r="B12" t="n">
-        <v>97874</v>
+        <v>96814</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567401</v>
+        <v>567358</v>
       </c>
       <c r="R12" t="n">
-        <v>7241831</v>
+        <v>7241988</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1932,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916053</v>
+        <v>118916045</v>
       </c>
       <c r="B13" t="n">
-        <v>96814</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,25 +1944,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567358</v>
+        <v>567294</v>
       </c>
       <c r="R13" t="n">
-        <v>7241988</v>
+        <v>7241774</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118916060</v>
+        <v>118916052</v>
       </c>
       <c r="B14" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567388</v>
+        <v>567274</v>
       </c>
       <c r="R14" t="n">
-        <v>7241872</v>
+        <v>7241984</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118916049</v>
+        <v>118916047</v>
       </c>
       <c r="B15" t="n">
-        <v>57306</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2192,7 +2192,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567260</v>
+        <v>567264</v>
       </c>
       <c r="R15" t="n">
-        <v>7241978</v>
+        <v>7241789</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 21423-2024 artfynd.xlsx
+++ b/artfynd/A 21423-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118916046</v>
+        <v>118916045</v>
       </c>
       <c r="B2" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567276</v>
+        <v>567294</v>
       </c>
       <c r="R2" t="n">
-        <v>7241770</v>
+        <v>7241774</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118916053</v>
+        <v>118916052</v>
       </c>
       <c r="B3" t="n">
-        <v>96819</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567358</v>
+        <v>567274</v>
       </c>
       <c r="R3" t="n">
-        <v>7241988</v>
+        <v>7241984</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,50 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118916052</v>
+        <v>118916049</v>
       </c>
       <c r="B4" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567274</v>
+        <v>567260</v>
       </c>
       <c r="R4" t="n">
-        <v>7241984</v>
+        <v>7241978</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,50 +1001,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118916051</v>
+        <v>118916060</v>
       </c>
       <c r="B5" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567260</v>
+        <v>567388</v>
       </c>
       <c r="R5" t="n">
-        <v>7241978</v>
+        <v>7241872</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,50 +1113,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118916062</v>
+        <v>118916043</v>
       </c>
       <c r="B6" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567401</v>
+        <v>567305</v>
       </c>
       <c r="R6" t="n">
-        <v>7241831</v>
+        <v>7241760</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118916060</v>
+        <v>118916044</v>
       </c>
       <c r="B7" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,16 +1236,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,7 +1256,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1285,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567388</v>
+        <v>567298</v>
       </c>
       <c r="R7" t="n">
-        <v>7241872</v>
+        <v>7241769</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,50 +1337,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118916055</v>
+        <v>118916046</v>
       </c>
       <c r="B8" t="n">
-        <v>96813</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567358</v>
+        <v>567276</v>
       </c>
       <c r="R8" t="n">
-        <v>7241959</v>
+        <v>7241770</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,12 +1452,7 @@
         <v>118916047</v>
       </c>
       <c r="B9" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,37 +1561,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118916045</v>
+        <v>118916053</v>
       </c>
       <c r="B10" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567294</v>
+        <v>567358</v>
       </c>
       <c r="R10" t="n">
-        <v>7241774</v>
+        <v>7241988</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,55 +1668,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118916043</v>
+        <v>118916055</v>
       </c>
       <c r="B11" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödingträskliden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567305</v>
+        <v>567358</v>
       </c>
       <c r="R11" t="n">
-        <v>7241760</v>
+        <v>7241959</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,37 +1775,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118916057</v>
+        <v>118916054</v>
       </c>
       <c r="B12" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567355</v>
+        <v>567357</v>
       </c>
       <c r="R12" t="n">
-        <v>7241955</v>
+        <v>7241980</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,15 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118916054</v>
+        <v>118916062</v>
       </c>
       <c r="B13" t="n">
-        <v>97879</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567357</v>
+        <v>567401</v>
       </c>
       <c r="R13" t="n">
-        <v>7241980</v>
+        <v>7241831</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,240 +1986,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>118916049</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Rödingträskliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>567260</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7241978</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>118916044</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Rödingträskliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>567298</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7241769</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>08:07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>08:07</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
